--- a/p-1.0.xlsx
+++ b/p-1.0.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GLAB-PC002\Desktop\sumo_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B393122-2AB1-4110-B057-46ACD5FB2B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85ED8994-36AF-4820-A0ED-A2BEA04116FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{37AB8F44-6CE5-491C-8134-0C6CCB608F37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37AB8F44-6CE5-491C-8134-0C6CCB608F37}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="p-1.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -492,14 +492,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3263,7 +3260,7 @@
       </c>
       <c r="U34" s="1"/>
       <c r="V34" t="b">
-        <f t="shared" ref="V34:V65" si="1">N90=AVERAGE(M:M)</f>
+        <f t="shared" ref="V34:V59" si="1">N90=AVERAGE(M:M)</f>
         <v>0</v>
       </c>
     </row>
@@ -4949,7 +4946,6 @@
         <f>AVERAGE(M:M)</f>
         <v>63.172413793103445</v>
       </c>
-      <c r="V60" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
